--- a/clinic_patients_file_updated.xlsx
+++ b/clinic_patients_file_updated.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anwari Ahmed\Desktop\employeesql\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AAEAE4-CDB8-487F-8077-79DB15B94C96}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="12" windowWidth="16092" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="53">
   <si>
     <t>PATIENT_ID</t>
   </si>
@@ -76,6 +70,9 @@
     <t>Adnan Bashir</t>
   </si>
   <si>
+    <t>Murawat Hussein</t>
+  </si>
+  <si>
     <t>Caries</t>
   </si>
   <si>
@@ -139,6 +136,9 @@
     <t>Composite Bonding</t>
   </si>
   <si>
+    <t>xla</t>
+  </si>
+  <si>
     <t>composite</t>
   </si>
   <si>
@@ -170,12 +170,6 @@
   </si>
   <si>
     <t>Composite Resin, Etchant, Light Cure</t>
-  </si>
-  <si>
-    <t>Murawat Hussein</t>
-  </si>
-  <si>
-    <t>xla</t>
   </si>
   <si>
     <t>gauze</t>
@@ -184,8 +178,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,19 +242,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -302,7 +288,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -334,27 +320,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -386,24 +354,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -579,11 +529,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,7 +556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>2</v>
       </c>
@@ -614,10 +564,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>3000</v>
@@ -626,10 +576,10 @@
         <v>3000</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>3</v>
       </c>
@@ -637,10 +587,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>2500</v>
@@ -649,10 +599,10 @@
         <v>2500</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>4</v>
       </c>
@@ -660,10 +610,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4">
         <v>3000</v>
@@ -672,10 +622,10 @@
         <v>2000</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>5</v>
       </c>
@@ -683,10 +633,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <v>8000</v>
@@ -695,10 +645,10 @@
         <v>8000</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>6</v>
       </c>
@@ -706,10 +656,10 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>9000</v>
@@ -718,10 +668,10 @@
         <v>6000</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>7</v>
       </c>
@@ -729,10 +679,10 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <v>7000</v>
@@ -741,10 +691,10 @@
         <v>7000</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>8</v>
       </c>
@@ -752,10 +702,10 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8">
         <v>5000</v>
@@ -764,10 +714,10 @@
         <v>3000</v>
       </c>
       <c r="G8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>9</v>
       </c>
@@ -775,10 +725,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9">
         <v>15000</v>
@@ -787,10 +737,10 @@
         <v>10000</v>
       </c>
       <c r="G9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>10</v>
       </c>
@@ -798,10 +748,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10">
         <v>4000</v>
@@ -810,10 +760,10 @@
         <v>2000</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>11</v>
       </c>
@@ -821,10 +771,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>2000</v>
@@ -833,10 +783,10 @@
         <v>2000</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>12</v>
       </c>
@@ -844,10 +794,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12">
         <v>3500</v>
@@ -856,26 +806,282 @@
         <v>3500</v>
       </c>
       <c r="G12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13">
+        <v>3000</v>
+      </c>
+      <c r="F13">
+        <v>3000</v>
+      </c>
+      <c r="G13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <v>2500</v>
+      </c>
+      <c r="F14">
+        <v>2500</v>
+      </c>
+      <c r="G14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15">
+        <v>3000</v>
+      </c>
+      <c r="F15">
+        <v>2000</v>
+      </c>
+      <c r="G15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16">
+        <v>8000</v>
+      </c>
+      <c r="F16">
+        <v>8000</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17">
+        <v>9000</v>
+      </c>
+      <c r="F17">
+        <v>6000</v>
+      </c>
+      <c r="G17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18">
+        <v>7000</v>
+      </c>
+      <c r="F18">
+        <v>7000</v>
+      </c>
+      <c r="G18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19">
+        <v>5000</v>
+      </c>
+      <c r="F19">
+        <v>3000</v>
+      </c>
+      <c r="G19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20">
+        <v>15000</v>
+      </c>
+      <c r="F20">
+        <v>10000</v>
+      </c>
+      <c r="G20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21">
+        <v>4000</v>
+      </c>
+      <c r="F21">
+        <v>2000</v>
+      </c>
+      <c r="G21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22">
+        <v>2000</v>
+      </c>
+      <c r="F22">
+        <v>2000</v>
+      </c>
+      <c r="G22" t="s">
         <v>50</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23">
+        <v>3500</v>
+      </c>
+      <c r="F23">
+        <v>3500</v>
+      </c>
+      <c r="G23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
         <v>18</v>
       </c>
-      <c r="D13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13">
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24">
         <v>2000</v>
       </c>
-      <c r="F13">
+      <c r="F24">
         <v>2000</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G24" t="s">
         <v>52</v>
       </c>
     </row>
